--- a/samples/ss_sumbagteng_ingest.xlsx
+++ b/samples/ss_sumbagteng_ingest.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,6 +590,21 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GABUNGAN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gabungan Riau, Sumbar &amp; Jambi</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>18</v>
       </c>
     </row>
@@ -741,25 +756,16 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -816,21 +822,16 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -869,25 +870,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -944,21 +936,16 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1015,21 +1002,16 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1068,27 +1050,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1127,25 +1101,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1184,21 +1149,14 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1247,25 +1205,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1304,27 +1253,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1363,25 +1304,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1420,27 +1352,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1479,25 +1403,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1536,27 +1451,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1595,25 +1502,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1652,25 +1550,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1709,27 +1598,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1768,27 +1649,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1827,27 +1700,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1886,27 +1751,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -1945,27 +1802,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2004,27 +1853,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2063,27 +1904,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2122,27 +1955,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2181,27 +2006,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2240,27 +2057,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2299,27 +2108,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2358,27 +2159,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2417,27 +2210,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2476,27 +2261,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2535,27 +2312,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2594,27 +2363,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2653,27 +2414,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2712,27 +2465,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Milik Pelanggan</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2771,25 +2516,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2846,21 +2582,16 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2917,21 +2648,16 @@
       <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -2970,27 +2696,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3029,25 +2747,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3104,21 +2813,16 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3175,21 +2879,16 @@
       <c r="J42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3228,27 +2927,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3287,25 +2978,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3362,21 +3044,16 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3415,27 +3092,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3474,25 +3143,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3531,25 +3191,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3588,25 +3239,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3645,27 +3287,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3704,25 +3338,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3761,25 +3386,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3818,25 +3434,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3875,27 +3482,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3934,25 +3533,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -3991,25 +3581,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4048,25 +3629,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4105,25 +3677,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4162,27 +3725,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
         <v>1</v>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4221,27 +3776,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
         <v>1</v>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4280,27 +3827,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
         <v>1</v>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4339,27 +3878,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
         <v>1</v>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4398,27 +3929,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="n">
         <v>1</v>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4457,27 +3980,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4516,27 +4031,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
         <v>1</v>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4575,27 +4082,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
         <v>1</v>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4634,25 +4133,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4691,27 +4181,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
         <v>1</v>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4750,27 +4232,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
         <v>1</v>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4809,27 +4283,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
         <v>1</v>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4868,27 +4334,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
         <v>1</v>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4927,27 +4385,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
         <v>1</v>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -4986,27 +4436,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
         <v>1</v>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5045,27 +4487,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
         <v>1</v>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5104,27 +4538,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
         <v>1</v>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5163,25 +4589,16 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5238,21 +4655,16 @@
       <c r="J77" t="n">
         <v>1</v>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5291,25 +4703,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5366,21 +4769,16 @@
       <c r="J79" t="n">
         <v>1</v>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5437,21 +4835,16 @@
       <c r="J80" t="n">
         <v>1</v>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5490,27 +4883,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="n">
         <v>1</v>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5549,25 +4934,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5624,21 +5000,16 @@
       <c r="J83" t="n">
         <v>1</v>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5695,21 +5066,16 @@
       <c r="J84" t="n">
         <v>1</v>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5748,27 +5114,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
         <v>1</v>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5807,25 +5165,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5882,21 +5231,16 @@
       <c r="J87" t="n">
         <v>1</v>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -5953,21 +5297,16 @@
       <c r="J88" t="n">
         <v>1</v>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6006,27 +5345,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
         <v>1</v>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6065,25 +5396,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6122,27 +5444,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
         <v>1</v>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6181,25 +5495,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6238,31 +5543,24 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
         <v>1</v>
       </c>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>bus tanpa label di bawah PLTMG Sei Gelam</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6301,25 +5599,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6358,27 +5647,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
         <v>1</v>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6417,27 +5698,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="n">
         <v>1</v>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6476,27 +5749,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="n">
         <v>1</v>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6535,27 +5800,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="n">
         <v>1</v>
       </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6594,27 +5851,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="n">
         <v>1</v>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6653,27 +5902,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="n">
         <v>1</v>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6712,27 +5953,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
         <v>1</v>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6771,27 +6004,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
         <v>1</v>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6830,27 +6055,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="n">
         <v>1</v>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -6967,7 +6184,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Outlet PLTMG/G Balai Pungut 1</t>
@@ -6988,7 +6204,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -7002,8 +6217,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7030,7 +6243,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Outlet PLTA Koto Panjang</t>
@@ -7051,7 +6263,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -7065,8 +6276,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7093,7 +6302,6 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Outlet PLTG/MG Teluk Lembu</t>
@@ -7114,7 +6322,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -7128,8 +6335,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7156,7 +6361,6 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Outlet PLTU Tenayan</t>
@@ -7177,7 +6381,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -7191,8 +6394,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7219,7 +6420,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Outlet PLTGU Riau</t>
@@ -7240,7 +6440,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>1</v>
       </c>
@@ -7254,8 +6453,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7282,7 +6479,6 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Outlet PLTU Ombilin</t>
@@ -7303,7 +6499,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -7317,8 +6512,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7345,7 +6538,6 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Outlet PLTA Maninjau</t>
@@ -7366,7 +6558,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -7380,8 +6571,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7408,7 +6597,6 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Outlet PLTA Singkarak</t>
@@ -7429,7 +6617,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -7443,8 +6630,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7471,7 +6656,6 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Outlet PLTG Pauh Limo</t>
@@ -7492,7 +6676,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>1</v>
       </c>
@@ -7506,8 +6689,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7534,7 +6715,6 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Outlet PLTU/G Teluk Sirih</t>
@@ -7555,7 +6735,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -7569,8 +6748,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7597,7 +6774,6 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Outlet PLTP Muara Labuh</t>
@@ -7618,7 +6794,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>1</v>
       </c>
@@ -7632,8 +6807,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7660,7 +6833,6 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Outlet PLTG Payo Selincah</t>
@@ -7681,7 +6853,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -7695,8 +6866,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7723,7 +6892,6 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Outlet PLTMG Sei Gelam</t>
@@ -7744,7 +6912,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>1</v>
       </c>
@@ -7758,8 +6925,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7786,7 +6951,6 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Outlet PLTA Merangin</t>
@@ -7807,7 +6971,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1</v>
       </c>
@@ -7821,8 +6984,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7874,7 +7035,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -7888,8 +7048,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -7941,7 +7099,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -7955,8 +7112,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8008,7 +7163,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -8022,8 +7176,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8050,7 +7202,6 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>SUTT 150 kV Teluk Lembu - Garuda Sakti</t>
@@ -8071,7 +7222,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -8085,8 +7235,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8113,7 +7261,6 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>SUTT 150 kV Teluk Lembu - Tenayan</t>
@@ -8134,7 +7281,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -8148,8 +7294,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8201,7 +7345,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -8215,8 +7358,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8243,7 +7384,6 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>SUTT 150 kV Tenayan - Perawang</t>
@@ -8264,7 +7404,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -8278,8 +7417,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8306,7 +7443,6 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>SUTT 150 kV Riau - Pasir Putih</t>
@@ -8327,7 +7463,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -8341,8 +7476,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8394,7 +7527,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -8408,8 +7540,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8436,7 +7566,6 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>SUTT 150 kV Perawang - New Garuda Sakti</t>
@@ -8457,7 +7586,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -8471,8 +7599,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8499,7 +7625,6 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>SUTT 150 kV Duri - Bagan Batu</t>
@@ -8520,7 +7645,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -8534,8 +7658,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8587,7 +7709,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -8601,8 +7722,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8654,7 +7773,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -8668,8 +7786,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8696,7 +7812,6 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>SUTT 150 kV Bangkinang - Pasir Pangaraian</t>
@@ -8717,7 +7832,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -8731,8 +7845,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8759,7 +7871,6 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>SUTT 150 kV Garuda Sakti - Kota Pekanbaru</t>
@@ -8780,7 +7891,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -8794,8 +7904,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8822,7 +7930,6 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>SUTT 150 kV Garuda Sakti - Pasir Putih</t>
@@ -8843,7 +7950,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -8857,8 +7963,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8885,7 +7989,6 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>SUTT 150 kV Pasir Putih - Pangkalan Kerinci</t>
@@ -8906,7 +8009,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -8920,8 +8022,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -8948,7 +8048,6 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>SUTT 150 kV Pangkalan Kerinci - Rengat</t>
@@ -8969,7 +8068,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -8983,8 +8081,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9011,7 +8107,6 @@
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>SUTT 150 kV Teluk Kuantan - Rengat</t>
@@ -9032,7 +8127,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -9046,8 +8140,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9074,7 +8166,6 @@
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>SUTT 150 kV Rengat - Tembilahan</t>
@@ -9095,7 +8186,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -9109,8 +8199,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9137,7 +8225,6 @@
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>SUTT 150 kV Dumai - KID</t>
@@ -9158,7 +8245,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>2</v>
       </c>
@@ -9172,8 +8258,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9200,7 +8284,6 @@
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>SUTT 150 kV Dumai - Bagan Siapi-api</t>
@@ -9221,7 +8304,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>2</v>
       </c>
@@ -9235,8 +8317,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9263,7 +8343,6 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>SUTT 150 kV KID - Pakning</t>
@@ -9284,7 +8363,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>1</v>
       </c>
@@ -9298,8 +8376,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9326,7 +8402,6 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>SUTT 150 kV KID - Wina</t>
@@ -9347,7 +8422,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>1</v>
       </c>
@@ -9361,8 +8435,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9389,7 +8461,6 @@
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>SUTT 150 kV Koto Panjang - Payakumbuh</t>
@@ -9410,7 +8481,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -9424,8 +8494,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9477,7 +8545,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -9491,8 +8558,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9519,7 +8584,6 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>SUTT 150 kV Payakumbuh - Padang Luar</t>
@@ -9540,7 +8604,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -9554,8 +8617,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9582,7 +8643,6 @@
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>SUTT 150 kV Payakumbuh - Batu Sangkar</t>
@@ -9603,7 +8663,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -9617,8 +8676,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9645,7 +8702,6 @@
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>SUTT 150 kV Ombilin - Batu Sangkar</t>
@@ -9666,7 +8722,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -9680,8 +8735,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9708,7 +8761,6 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>SUTT 150 kV Ombilin - Kiliranjao</t>
@@ -9729,7 +8781,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -9743,8 +8794,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9796,7 +8845,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>1</v>
       </c>
@@ -9810,8 +8858,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9863,7 +8909,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>1</v>
       </c>
@@ -9877,8 +8922,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9905,7 +8948,6 @@
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>SUTT 150 kV Salak - Solok</t>
@@ -9926,7 +8968,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>1</v>
       </c>
@@ -9940,8 +8981,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -9968,7 +9007,6 @@
       <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>SUTT 150 kV Indarung - Solok</t>
@@ -9989,7 +9027,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>1</v>
       </c>
@@ -10003,8 +9040,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10031,7 +9066,6 @@
       <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>SUTT 150 kV Batu Sangkar - Padang Panjang</t>
@@ -10052,7 +9086,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>1</v>
       </c>
@@ -10066,8 +9099,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10094,7 +9125,6 @@
       <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>SUTT 150 kV Singkarak - Padang Panjang</t>
@@ -10115,7 +9145,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>1</v>
       </c>
@@ -10129,8 +9158,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10182,7 +9209,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>2</v>
       </c>
@@ -10196,8 +9222,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10249,7 +9273,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>2</v>
       </c>
@@ -10263,8 +9286,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10291,7 +9312,6 @@
       <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>SUTT 150 kV Simpang Empat - Pasaman</t>
@@ -10312,7 +9332,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>2</v>
       </c>
@@ -10326,8 +9345,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10354,7 +9371,6 @@
       <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>SUTT 150 kV Maninjau - Pariaman</t>
@@ -10375,7 +9391,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>1</v>
       </c>
@@ -10389,8 +9404,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10417,7 +9430,6 @@
       <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>SUTT 150 kV Pariaman - Lubuk Alung</t>
@@ -10438,7 +9450,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>1</v>
       </c>
@@ -10452,8 +9463,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10480,7 +9489,6 @@
       <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>SUTT 150 kV Maninjau - Lubuk Alung</t>
@@ -10501,7 +9509,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>1</v>
       </c>
@@ -10515,8 +9522,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10543,7 +9548,6 @@
       <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>SUTT 150 kV Maninjau - Padang Luar</t>
@@ -10564,7 +9568,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>2</v>
       </c>
@@ -10578,8 +9581,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10606,7 +9607,6 @@
       <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>SUTT 150 kV Lubuk Alung - PIP</t>
@@ -10627,7 +9627,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>1</v>
       </c>
@@ -10641,8 +9640,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10669,7 +9666,6 @@
       <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>SUTT 150 kV Pauh Limo - Lubuk Alung</t>
@@ -10690,7 +9686,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>1</v>
       </c>
@@ -10704,8 +9699,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10732,7 +9725,6 @@
       <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>SUTT 150 kV Pauh Limo - PIP</t>
@@ -10753,7 +9745,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>1</v>
       </c>
@@ -10767,8 +9758,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10820,7 +9809,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>2</v>
       </c>
@@ -10834,8 +9822,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10887,7 +9873,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>2</v>
       </c>
@@ -10901,8 +9886,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10954,7 +9937,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>2</v>
       </c>
@@ -10968,8 +9950,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -10996,7 +9976,6 @@
       <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>SUTT 150 kV Bungus - Teluk Sirih</t>
@@ -11017,7 +9996,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -11031,8 +10009,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11059,7 +10035,6 @@
       <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>SUTT 150 kV Teluk Sirih - Kambang</t>
@@ -11080,7 +10055,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>2</v>
       </c>
@@ -11094,8 +10068,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11122,7 +10094,6 @@
       <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>SUTT 150 kV Kambang - Tapan</t>
@@ -11143,7 +10114,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>2</v>
       </c>
@@ -11157,8 +10127,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11185,7 +10153,6 @@
       <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>SUTT 150 kV Tapan - Muko-Muko</t>
@@ -11206,7 +10173,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>2</v>
       </c>
@@ -11220,8 +10186,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11248,7 +10212,6 @@
       <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>SUTT 150 kV PLTP Muara Labuh - Muara Labuh</t>
@@ -11269,7 +10232,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>2</v>
       </c>
@@ -11283,8 +10245,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11311,7 +10271,6 @@
       <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sungai Rumbai - Muara Labuh</t>
@@ -11332,7 +10291,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>2</v>
       </c>
@@ -11346,8 +10304,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11374,7 +10330,6 @@
       <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>SUTT 150 kV Muara Bungo - Muara Tebo</t>
@@ -11395,7 +10350,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>2</v>
       </c>
@@ -11409,8 +10363,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11437,7 +10389,6 @@
       <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
           <t>SUTT 150 kV Muara Tebo - Muara Bulian</t>
@@ -11458,7 +10409,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>2</v>
       </c>
@@ -11472,8 +10422,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11525,7 +10473,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>1</v>
       </c>
@@ -11539,8 +10486,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11567,7 +10512,6 @@
       <c r="A74" t="n">
         <v>73</v>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>SUTT 150 kV Muara Bulian - Sarolangun</t>
@@ -11588,7 +10532,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>2</v>
       </c>
@@ -11602,8 +10545,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11655,7 +10596,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>1</v>
       </c>
@@ -11669,8 +10609,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11722,7 +10660,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>2</v>
       </c>
@@ -11736,8 +10673,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11789,7 +10724,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>1</v>
       </c>
@@ -11803,8 +10737,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11856,7 +10788,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -11870,8 +10801,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11898,7 +10827,6 @@
       <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
           <t>SUTT 150 kV New Aurduri - Sei Gelam</t>
@@ -11919,7 +10847,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>2</v>
       </c>
@@ -11933,8 +10860,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -11961,7 +10886,6 @@
       <c r="A80" t="n">
         <v>79</v>
       </c>
-      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
           <t>SUTT 150 kV Payo Selincah - Muara Sabak</t>
@@ -11982,7 +10906,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>1</v>
       </c>
@@ -11996,8 +10919,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -12049,7 +10970,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>1</v>
       </c>
@@ -12063,8 +10983,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -12116,7 +11034,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>1</v>
       </c>
@@ -12130,8 +11047,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -12158,7 +11073,6 @@
       <c r="A83" t="n">
         <v>82</v>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
           <t>SUTT 150 kV Muara Sabak - Kuala Tungkal</t>
@@ -12179,7 +11093,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -12193,8 +11106,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -12221,7 +11132,6 @@
       <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
           <t>SUTT 150 kV Kuala Tungkal - Pelabuhan Dagang</t>
@@ -12242,7 +11152,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>2</v>
       </c>
@@ -12256,8 +11165,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
           <t>Sumbagteng</t>
@@ -12383,7 +11290,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>RIAU</t>
@@ -12427,7 +11333,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>SUMBAR</t>
@@ -12471,7 +11376,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>SUMBAR</t>
@@ -12515,7 +11419,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>SUMBAR</t>
@@ -12559,7 +11462,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>JAMBI</t>
@@ -12603,7 +11505,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>JAMBI</t>
